--- a/artfynd/A 9151-2026 artfynd.xlsx
+++ b/artfynd/A 9151-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,4246 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131461677</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>407680</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6780356</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skalade smågranar</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131461705</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>407866</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6780294</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131461707</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>407822</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6780311</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131461728</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>407711</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6780190</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131461680</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>407774</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6780215</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131461690</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91837</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>407840</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6780220</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131461702</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>407856</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6780250</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131461698</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>407676</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6780219</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131461730</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>407809</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6780292</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131461661</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83229</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>407677</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6780219</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131461729</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>407819</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6780213</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131461697</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>407669</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6780222</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131461664</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83229</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>407627</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6780327</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131461711</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>407652</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6780335</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131461674</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>407700</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6780198</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131461700</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>407739</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6780193</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131461710</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>407751</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6780279</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131461703</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>407870</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6780257</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131461704</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>407887</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6780271</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131461662</v>
+      </c>
+      <c r="B22" t="n">
+        <v>83229</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>407869</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6780285</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131461696</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>407659</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6780230</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131461709</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>407776</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6780290</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131461727</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>407639</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6780228</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131461713</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>407617</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6780319</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131461712</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>407634</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6780338</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131461695</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>407614</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6780228</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131461675</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>407786</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6780235</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131461726</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>407594</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6780218</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131461665</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91780</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>407622</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6780319</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131461706</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>407831</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6780313</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131461689</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91837</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>407777</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6780230</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131461736</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>407604</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6780314</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131461708</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>407812</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6780302</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131461701</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>407853</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6780222</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131461714</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>407612</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6780318</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131461672</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>407684</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6780323</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ovalt bohål i gammal tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131461663</v>
+      </c>
+      <c r="B39" t="n">
+        <v>83229</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>407743</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6780290</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131461731</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>407622</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6780319</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131461699</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79249</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>407692</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6780214</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9151-2026 artfynd.xlsx
+++ b/artfynd/A 9151-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>131461677</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>131461705</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>131461707</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>131461728</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131461680</v>
+        <v>131461690</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,39 +1243,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407774</v>
+        <v>407840</v>
       </c>
       <c r="R7" t="n">
-        <v>6780215</v>
+        <v>6780220</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,12 +1308,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131461690</v>
+        <v>131461702</v>
       </c>
       <c r="B8" t="n">
-        <v>91837</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,19 +1346,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1380,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407840</v>
+        <v>407856</v>
       </c>
       <c r="R8" t="n">
-        <v>6780220</v>
+        <v>6780250</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1405,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,7 +1415,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131461702</v>
+        <v>131461680</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1453,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407856</v>
+        <v>407774</v>
       </c>
       <c r="R9" t="n">
-        <v>6780250</v>
+        <v>6780215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,7 +1527,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,7 +1562,7 @@
         <v>131461698</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131461730</v>
+        <v>131461661</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>83230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,39 +1677,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407809</v>
+        <v>407677</v>
       </c>
       <c r="R11" t="n">
-        <v>6780292</v>
+        <v>6780219</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,7 +1736,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,7 +1746,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131461661</v>
+        <v>131461730</v>
       </c>
       <c r="B12" t="n">
-        <v>83229</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,34 +1784,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407677</v>
+        <v>407809</v>
       </c>
       <c r="R12" t="n">
-        <v>6780219</v>
+        <v>6780292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1888,7 +1888,7 @@
         <v>131461729</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>131461697</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>131461664</v>
       </c>
       <c r="B15" t="n">
-        <v>83229</v>
+        <v>83230</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,10 +2211,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131461711</v>
+        <v>131461674</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,34 +2222,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407652</v>
+        <v>407700</v>
       </c>
       <c r="R16" t="n">
-        <v>6780335</v>
+        <v>6780198</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,7 +2286,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2291,7 +2296,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2318,10 +2323,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131461674</v>
+        <v>131461711</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,39 +2334,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407700</v>
+        <v>407652</v>
       </c>
       <c r="R17" t="n">
-        <v>6780198</v>
+        <v>6780335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,7 +2433,7 @@
         <v>131461700</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>131461710</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>131461703</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>131461704</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>131461662</v>
       </c>
       <c r="B22" t="n">
-        <v>83229</v>
+        <v>83230</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>131461696</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>131461709</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>131461727</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>131461713</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>131461712</v>
       </c>
       <c r="B27" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131461695</v>
+        <v>131461675</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3516,34 +3516,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407614</v>
+        <v>407786</v>
       </c>
       <c r="R28" t="n">
-        <v>6780228</v>
+        <v>6780235</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,7 +3580,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3585,7 +3590,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3612,10 +3617,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131461675</v>
+        <v>131461695</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3623,39 +3628,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407786</v>
+        <v>407614</v>
       </c>
       <c r="R29" t="n">
-        <v>6780235</v>
+        <v>6780228</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3727,7 +3727,7 @@
         <v>131461726</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>131461665</v>
       </c>
       <c r="B31" t="n">
-        <v>91780</v>
+        <v>91781</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>131461706</v>
       </c>
       <c r="B32" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>131461689</v>
       </c>
       <c r="B33" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,50 +4153,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131461736</v>
+        <v>131461708</v>
       </c>
       <c r="B34" t="n">
-        <v>5177</v>
+        <v>79250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>407604</v>
+        <v>407812</v>
       </c>
       <c r="R34" t="n">
-        <v>6780314</v>
+        <v>6780302</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4228,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4238,7 +4233,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4265,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131461708</v>
+        <v>131461701</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4300,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>407812</v>
+        <v>407853</v>
       </c>
       <c r="R35" t="n">
-        <v>6780302</v>
+        <v>6780222</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4330,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4345,7 +4340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4372,10 +4367,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131461701</v>
+        <v>131461714</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4407,10 +4402,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407853</v>
+        <v>407612</v>
       </c>
       <c r="R36" t="n">
-        <v>6780222</v>
+        <v>6780318</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4442,7 +4437,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4452,7 +4447,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4479,10 +4474,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131461714</v>
+        <v>131461672</v>
       </c>
       <c r="B37" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4490,34 +4485,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407612</v>
+        <v>407684</v>
       </c>
       <c r="R37" t="n">
-        <v>6780318</v>
+        <v>6780323</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4559,7 +4559,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ovalt bohål i gammal tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4586,38 +4591,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131461672</v>
+        <v>131461736</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>5177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4626,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407684</v>
+        <v>407604</v>
       </c>
       <c r="R38" t="n">
-        <v>6780323</v>
+        <v>6780314</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4661,7 +4666,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4671,12 +4676,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ovalt bohål i gammal tall</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4703,10 +4703,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131461663</v>
+        <v>131461731</v>
       </c>
       <c r="B39" t="n">
-        <v>83229</v>
+        <v>57888</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4714,34 +4714,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407743</v>
+        <v>407622</v>
       </c>
       <c r="R39" t="n">
-        <v>6780290</v>
+        <v>6780319</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4773,7 +4778,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4783,7 +4788,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4810,10 +4815,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131461731</v>
+        <v>131461663</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>83230</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4821,39 +4826,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407622</v>
+        <v>407743</v>
       </c>
       <c r="R40" t="n">
-        <v>6780319</v>
+        <v>6780290</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4925,7 +4925,7 @@
         <v>131461699</v>
       </c>
       <c r="B41" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 9151-2026 artfynd.xlsx
+++ b/artfynd/A 9151-2026 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131461677</v>
+        <v>131461705</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,39 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407680</v>
+        <v>407866</v>
       </c>
       <c r="R3" t="n">
-        <v>6780356</v>
+        <v>6780294</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +859,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,12 +869,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skalade smågranar</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131461705</v>
+        <v>131461707</v>
       </c>
       <c r="B4" t="n">
         <v>79250</v>
@@ -941,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407866</v>
+        <v>407822</v>
       </c>
       <c r="R4" t="n">
-        <v>6780294</v>
+        <v>6780311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +976,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131461707</v>
+        <v>131461677</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,34 +1014,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407822</v>
+        <v>407680</v>
       </c>
       <c r="R5" t="n">
-        <v>6780311</v>
+        <v>6780356</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1093,7 +1088,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Skalade smågranar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2211,10 +2211,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131461674</v>
+        <v>131461711</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,39 +2222,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407700</v>
+        <v>407652</v>
       </c>
       <c r="R16" t="n">
-        <v>6780198</v>
+        <v>6780335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,7 +2281,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2296,7 +2291,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,7 +2318,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131461711</v>
+        <v>131461700</v>
       </c>
       <c r="B17" t="n">
         <v>79250</v>
@@ -2358,10 +2353,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407652</v>
+        <v>407739</v>
       </c>
       <c r="R17" t="n">
-        <v>6780335</v>
+        <v>6780193</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,7 +2388,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2403,7 +2398,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,7 +2425,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131461700</v>
+        <v>131461710</v>
       </c>
       <c r="B18" t="n">
         <v>79250</v>
@@ -2465,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407739</v>
+        <v>407751</v>
       </c>
       <c r="R18" t="n">
-        <v>6780193</v>
+        <v>6780279</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2500,7 +2495,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2510,7 +2505,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2537,10 +2532,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131461710</v>
+        <v>131461674</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,34 +2543,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407751</v>
+        <v>407700</v>
       </c>
       <c r="R19" t="n">
-        <v>6780279</v>
+        <v>6780198</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3505,10 +3505,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131461675</v>
+        <v>131461695</v>
       </c>
       <c r="B28" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3516,39 +3516,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407786</v>
+        <v>407614</v>
       </c>
       <c r="R28" t="n">
-        <v>6780235</v>
+        <v>6780228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3580,7 +3575,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3590,7 +3585,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3617,10 +3612,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131461695</v>
+        <v>131461675</v>
       </c>
       <c r="B29" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,34 +3623,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407614</v>
+        <v>407786</v>
       </c>
       <c r="R29" t="n">
-        <v>6780228</v>
+        <v>6780235</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4474,38 +4474,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131461672</v>
+        <v>131461736</v>
       </c>
       <c r="B37" t="n">
-        <v>57885</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407684</v>
+        <v>407604</v>
       </c>
       <c r="R37" t="n">
-        <v>6780323</v>
+        <v>6780314</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4559,12 +4559,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ovalt bohål i gammal tall</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4591,38 +4586,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131461736</v>
+        <v>131461672</v>
       </c>
       <c r="B38" t="n">
-        <v>5177</v>
+        <v>57885</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407604</v>
+        <v>407684</v>
       </c>
       <c r="R38" t="n">
-        <v>6780314</v>
+        <v>6780323</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4666,7 +4661,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4676,7 +4671,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ovalt bohål i gammal tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4703,10 +4703,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131461731</v>
+        <v>131461663</v>
       </c>
       <c r="B39" t="n">
-        <v>57888</v>
+        <v>83230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4714,39 +4714,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407622</v>
+        <v>407743</v>
       </c>
       <c r="R39" t="n">
-        <v>6780319</v>
+        <v>6780290</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4778,7 +4773,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4788,7 +4783,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4815,10 +4810,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131461663</v>
+        <v>131461699</v>
       </c>
       <c r="B40" t="n">
-        <v>83230</v>
+        <v>79250</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4826,21 +4821,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4850,10 +4845,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407743</v>
+        <v>407692</v>
       </c>
       <c r="R40" t="n">
-        <v>6780290</v>
+        <v>6780214</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4885,7 +4880,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4895,7 +4890,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4922,10 +4917,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131461699</v>
+        <v>131461731</v>
       </c>
       <c r="B41" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,34 +4928,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407692</v>
+        <v>407622</v>
       </c>
       <c r="R41" t="n">
-        <v>6780214</v>
+        <v>6780319</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 9151-2026 artfynd.xlsx
+++ b/artfynd/A 9151-2026 artfynd.xlsx
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131461702</v>
+        <v>131461680</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,34 +1346,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407856</v>
+        <v>407774</v>
       </c>
       <c r="R8" t="n">
-        <v>6780250</v>
+        <v>6780215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1415,7 +1420,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131461680</v>
+        <v>131461702</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,39 +1463,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407774</v>
+        <v>407856</v>
       </c>
       <c r="R9" t="n">
-        <v>6780215</v>
+        <v>6780250</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,12 +1532,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 9151-2026 artfynd.xlsx
+++ b/artfynd/A 9151-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>131461705</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>131461707</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>131461677</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>131461728</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131461690</v>
+        <v>131461680</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,30 +1243,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407840</v>
+        <v>407774</v>
       </c>
       <c r="R7" t="n">
-        <v>6780220</v>
+        <v>6780215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,7 +1317,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131461680</v>
+        <v>131461702</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,39 +1360,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407774</v>
+        <v>407856</v>
       </c>
       <c r="R8" t="n">
-        <v>6780215</v>
+        <v>6780250</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,12 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131461702</v>
+        <v>131461690</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>91841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,23 +1467,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407856</v>
+        <v>407840</v>
       </c>
       <c r="R9" t="n">
-        <v>6780250</v>
+        <v>6780220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131461698</v>
+        <v>131461730</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,34 +1570,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407676</v>
+        <v>407809</v>
       </c>
       <c r="R10" t="n">
-        <v>6780219</v>
+        <v>6780292</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1639,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1666,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131461661</v>
+        <v>131461729</v>
       </c>
       <c r="B11" t="n">
-        <v>83230</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,34 +1682,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407677</v>
+        <v>407819</v>
       </c>
       <c r="R11" t="n">
-        <v>6780219</v>
+        <v>6780213</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1746,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1746,7 +1756,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,10 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131461730</v>
+        <v>131461698</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,39 +1794,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407809</v>
+        <v>407676</v>
       </c>
       <c r="R12" t="n">
-        <v>6780292</v>
+        <v>6780219</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1858,7 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,10 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131461729</v>
+        <v>131461661</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>83233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,39 +1901,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407819</v>
+        <v>407677</v>
       </c>
       <c r="R13" t="n">
-        <v>6780213</v>
+        <v>6780219</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,7 +2000,7 @@
         <v>131461697</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>131461664</v>
       </c>
       <c r="B15" t="n">
-        <v>83230</v>
+        <v>83233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>131461711</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>131461700</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>131461710</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>131461674</v>
       </c>
       <c r="B19" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>131461703</v>
       </c>
       <c r="B20" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>131461704</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>131461662</v>
       </c>
       <c r="B22" t="n">
-        <v>83230</v>
+        <v>83233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>131461696</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>131461709</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>131461727</v>
       </c>
       <c r="B25" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>131461713</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>131461712</v>
       </c>
       <c r="B27" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131461695</v>
+        <v>131461726</v>
       </c>
       <c r="B28" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3516,34 +3516,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407614</v>
+        <v>407594</v>
       </c>
       <c r="R28" t="n">
-        <v>6780228</v>
+        <v>6780218</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,7 +3580,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3585,7 +3590,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3612,10 +3617,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131461675</v>
+        <v>131461695</v>
       </c>
       <c r="B29" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3623,39 +3628,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407786</v>
+        <v>407614</v>
       </c>
       <c r="R29" t="n">
-        <v>6780235</v>
+        <v>6780228</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3724,7 +3724,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131461726</v>
+        <v>131461675</v>
       </c>
       <c r="B30" t="n">
         <v>57888</v>
@@ -3735,16 +3735,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407594</v>
+        <v>407786</v>
       </c>
       <c r="R30" t="n">
-        <v>6780218</v>
+        <v>6780235</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3839,7 +3839,7 @@
         <v>131461665</v>
       </c>
       <c r="B31" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>131461706</v>
       </c>
       <c r="B32" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>131461689</v>
       </c>
       <c r="B33" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>131461708</v>
       </c>
       <c r="B34" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>131461701</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>131461714</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,38 +4474,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131461736</v>
+        <v>131461672</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>57888</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407604</v>
+        <v>407684</v>
       </c>
       <c r="R37" t="n">
-        <v>6780314</v>
+        <v>6780323</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4559,7 +4559,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ovalt bohål i gammal tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4586,38 +4591,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131461672</v>
+        <v>131461736</v>
       </c>
       <c r="B38" t="n">
-        <v>57885</v>
+        <v>5177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4626,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407684</v>
+        <v>407604</v>
       </c>
       <c r="R38" t="n">
-        <v>6780323</v>
+        <v>6780314</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4661,7 +4666,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4671,12 +4676,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ovalt bohål i gammal tall</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4706,7 +4706,7 @@
         <v>131461663</v>
       </c>
       <c r="B39" t="n">
-        <v>83230</v>
+        <v>83233</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>131461699</v>
       </c>
       <c r="B40" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>131461731</v>
       </c>
       <c r="B41" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 9151-2026 artfynd.xlsx
+++ b/artfynd/A 9151-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>131461705</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>131461707</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>131461677</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>131461728</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131461680</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131461702</v>
+        <v>131461690</v>
       </c>
       <c r="B8" t="n">
-        <v>79253</v>
+        <v>91842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,23 +1360,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1384,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407856</v>
+        <v>407840</v>
       </c>
       <c r="R8" t="n">
-        <v>6780250</v>
+        <v>6780220</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1425,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131461690</v>
+        <v>131461702</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,19 +1463,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407840</v>
+        <v>407856</v>
       </c>
       <c r="R9" t="n">
-        <v>6780220</v>
+        <v>6780250</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131461730</v>
+        <v>131461698</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,39 +1570,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407809</v>
+        <v>407676</v>
       </c>
       <c r="R10" t="n">
-        <v>6780292</v>
+        <v>6780219</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1629,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1639,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131461729</v>
+        <v>131461661</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>83234</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,39 +1677,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407819</v>
+        <v>407677</v>
       </c>
       <c r="R11" t="n">
-        <v>6780213</v>
+        <v>6780219</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1736,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1756,7 +1746,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131461698</v>
+        <v>131461730</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,34 +1784,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407676</v>
+        <v>407809</v>
       </c>
       <c r="R12" t="n">
-        <v>6780219</v>
+        <v>6780292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1848,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1858,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131461661</v>
+        <v>131461729</v>
       </c>
       <c r="B13" t="n">
-        <v>83233</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,34 +1896,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407677</v>
+        <v>407819</v>
       </c>
       <c r="R13" t="n">
-        <v>6780219</v>
+        <v>6780213</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,7 +2000,7 @@
         <v>131461697</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>131461664</v>
       </c>
       <c r="B15" t="n">
-        <v>83233</v>
+        <v>83234</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,10 +2211,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131461711</v>
+        <v>131461674</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,34 +2222,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407652</v>
+        <v>407700</v>
       </c>
       <c r="R16" t="n">
-        <v>6780335</v>
+        <v>6780198</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,7 +2286,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2291,7 +2296,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2318,10 +2323,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131461700</v>
+        <v>131461711</v>
       </c>
       <c r="B17" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2353,10 +2358,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407739</v>
+        <v>407652</v>
       </c>
       <c r="R17" t="n">
-        <v>6780193</v>
+        <v>6780335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,7 +2393,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2398,7 +2403,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2425,10 +2430,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131461710</v>
+        <v>131461700</v>
       </c>
       <c r="B18" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2460,10 +2465,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407751</v>
+        <v>407739</v>
       </c>
       <c r="R18" t="n">
-        <v>6780279</v>
+        <v>6780193</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,7 +2500,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2505,7 +2510,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,10 +2537,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131461674</v>
+        <v>131461710</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2543,39 +2548,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407700</v>
+        <v>407751</v>
       </c>
       <c r="R19" t="n">
-        <v>6780198</v>
+        <v>6780279</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2647,7 +2647,7 @@
         <v>131461703</v>
       </c>
       <c r="B20" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>131461704</v>
       </c>
       <c r="B21" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>131461662</v>
       </c>
       <c r="B22" t="n">
-        <v>83233</v>
+        <v>83234</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>131461696</v>
       </c>
       <c r="B23" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>131461709</v>
       </c>
       <c r="B24" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>131461727</v>
       </c>
       <c r="B25" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131461713</v>
+        <v>131461712</v>
       </c>
       <c r="B26" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407617</v>
+        <v>407634</v>
       </c>
       <c r="R26" t="n">
-        <v>6780319</v>
+        <v>6780338</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3398,10 +3398,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131461712</v>
+        <v>131461713</v>
       </c>
       <c r="B27" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>407634</v>
+        <v>407617</v>
       </c>
       <c r="R27" t="n">
-        <v>6780338</v>
+        <v>6780319</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3505,10 +3505,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131461726</v>
+        <v>131461695</v>
       </c>
       <c r="B28" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3516,39 +3516,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407594</v>
+        <v>407614</v>
       </c>
       <c r="R28" t="n">
-        <v>6780218</v>
+        <v>6780228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3580,7 +3575,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3590,7 +3585,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3617,10 +3612,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131461695</v>
+        <v>131461726</v>
       </c>
       <c r="B29" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,34 +3623,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407614</v>
+        <v>407594</v>
       </c>
       <c r="R29" t="n">
-        <v>6780228</v>
+        <v>6780218</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3727,7 +3727,7 @@
         <v>131461675</v>
       </c>
       <c r="B30" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>131461665</v>
       </c>
       <c r="B31" t="n">
-        <v>91784</v>
+        <v>91785</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>131461706</v>
       </c>
       <c r="B32" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>131461689</v>
       </c>
       <c r="B33" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>131461708</v>
       </c>
       <c r="B34" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>131461701</v>
       </c>
       <c r="B35" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>131461714</v>
       </c>
       <c r="B36" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,38 +4474,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131461672</v>
+        <v>131461736</v>
       </c>
       <c r="B37" t="n">
-        <v>57888</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407684</v>
+        <v>407604</v>
       </c>
       <c r="R37" t="n">
-        <v>6780323</v>
+        <v>6780314</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4559,12 +4559,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ovalt bohål i gammal tall</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4591,38 +4586,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131461736</v>
+        <v>131461672</v>
       </c>
       <c r="B38" t="n">
-        <v>5177</v>
+        <v>57889</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407604</v>
+        <v>407684</v>
       </c>
       <c r="R38" t="n">
-        <v>6780314</v>
+        <v>6780323</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4666,7 +4661,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4676,7 +4671,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ovalt bohål i gammal tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4706,7 +4706,7 @@
         <v>131461663</v>
       </c>
       <c r="B39" t="n">
-        <v>83233</v>
+        <v>83234</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>131461699</v>
       </c>
       <c r="B40" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>131461731</v>
       </c>
       <c r="B41" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 9151-2026 artfynd.xlsx
+++ b/artfynd/A 9151-2026 artfynd.xlsx
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131461680</v>
+        <v>131461690</v>
       </c>
       <c r="B7" t="n">
-        <v>57892</v>
+        <v>91842</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,39 +1243,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407774</v>
+        <v>407840</v>
       </c>
       <c r="R7" t="n">
-        <v>6780215</v>
+        <v>6780220</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,12 +1308,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131461690</v>
+        <v>131461702</v>
       </c>
       <c r="B8" t="n">
-        <v>91842</v>
+        <v>79254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,19 +1346,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1380,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407840</v>
+        <v>407856</v>
       </c>
       <c r="R8" t="n">
-        <v>6780220</v>
+        <v>6780250</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1405,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,7 +1415,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131461702</v>
+        <v>131461680</v>
       </c>
       <c r="B9" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1453,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407856</v>
+        <v>407774</v>
       </c>
       <c r="R9" t="n">
-        <v>6780250</v>
+        <v>6780215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,7 +1527,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2751,10 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131461704</v>
+        <v>131461727</v>
       </c>
       <c r="B21" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2762,34 +2762,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407887</v>
+        <v>407639</v>
       </c>
       <c r="R21" t="n">
-        <v>6780271</v>
+        <v>6780228</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2821,7 +2826,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2831,7 +2836,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2858,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131461662</v>
+        <v>131461704</v>
       </c>
       <c r="B22" t="n">
-        <v>83234</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,21 +2874,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2893,10 +2898,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407869</v>
+        <v>407887</v>
       </c>
       <c r="R22" t="n">
-        <v>6780285</v>
+        <v>6780271</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2928,7 +2933,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2938,7 +2943,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2965,10 +2970,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131461696</v>
+        <v>131461662</v>
       </c>
       <c r="B23" t="n">
-        <v>79254</v>
+        <v>83234</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2976,21 +2981,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3000,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407659</v>
+        <v>407869</v>
       </c>
       <c r="R23" t="n">
-        <v>6780230</v>
+        <v>6780285</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3035,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3045,7 +3050,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,7 +3077,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131461709</v>
+        <v>131461696</v>
       </c>
       <c r="B24" t="n">
         <v>79254</v>
@@ -3107,10 +3112,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407776</v>
+        <v>407659</v>
       </c>
       <c r="R24" t="n">
-        <v>6780290</v>
+        <v>6780230</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,7 +3147,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3152,7 +3157,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,10 +3184,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131461727</v>
+        <v>131461709</v>
       </c>
       <c r="B25" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,39 +3195,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407639</v>
+        <v>407776</v>
       </c>
       <c r="R25" t="n">
-        <v>6780228</v>
+        <v>6780290</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3291,7 +3291,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131461712</v>
+        <v>131461713</v>
       </c>
       <c r="B26" t="n">
         <v>79254</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407634</v>
+        <v>407617</v>
       </c>
       <c r="R26" t="n">
-        <v>6780338</v>
+        <v>6780319</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3398,7 +3398,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131461713</v>
+        <v>131461712</v>
       </c>
       <c r="B27" t="n">
         <v>79254</v>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>407617</v>
+        <v>407634</v>
       </c>
       <c r="R27" t="n">
-        <v>6780319</v>
+        <v>6780338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3505,10 +3505,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131461695</v>
+        <v>131461675</v>
       </c>
       <c r="B28" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3516,34 +3516,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407614</v>
+        <v>407786</v>
       </c>
       <c r="R28" t="n">
-        <v>6780228</v>
+        <v>6780235</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,7 +3580,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3585,7 +3590,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3612,10 +3617,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131461726</v>
+        <v>131461695</v>
       </c>
       <c r="B29" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3623,39 +3628,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407594</v>
+        <v>407614</v>
       </c>
       <c r="R29" t="n">
-        <v>6780218</v>
+        <v>6780228</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3724,10 +3724,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131461675</v>
+        <v>131461726</v>
       </c>
       <c r="B30" t="n">
-        <v>57889</v>
+        <v>57892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,16 +3735,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407786</v>
+        <v>407594</v>
       </c>
       <c r="R30" t="n">
-        <v>6780235</v>
+        <v>6780218</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
